--- a/output/Results - sem2 (Extended).xlsx
+++ b/output/Results - sem2 (Extended).xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1428" uniqueCount="290">
   <si>
     <t>Rank</t>
   </si>
@@ -550,6 +550,12 @@
     <t>PERERA H.A.J.I.</t>
   </si>
   <si>
+    <t>230229</t>
+  </si>
+  <si>
+    <t>HANSINDU M.M.A.D.</t>
+  </si>
+  <si>
     <t>230180</t>
   </si>
   <si>
@@ -592,12 +598,6 @@
     <t>ABEYWARDHANA T.C.W.</t>
   </si>
   <si>
-    <t>230229</t>
-  </si>
-  <si>
-    <t>HANSINDU M.M.A.D.</t>
-  </si>
-  <si>
     <t>230407</t>
   </si>
   <si>
@@ -742,6 +742,12 @@
     <t>HAKAM M.R.A.</t>
   </si>
   <si>
+    <t>230493</t>
+  </si>
+  <si>
+    <t>PIYUMAL N.P.P.</t>
+  </si>
+  <si>
     <t>230238</t>
   </si>
   <si>
@@ -766,130 +772,118 @@
     <t>NUWANAKA W.A.S.</t>
   </si>
   <si>
-    <t>230493</t>
-  </si>
-  <si>
-    <t>PIYUMAL N.P.P.</t>
+    <t>1(6.7%)</t>
+  </si>
+  <si>
+    <t>20(17.4%)</t>
+  </si>
+  <si>
+    <t>97(84.3%)</t>
+  </si>
+  <si>
+    <t>23(20.0%)</t>
+  </si>
+  <si>
+    <t>24(20.9%)</t>
+  </si>
+  <si>
+    <t>31(27.0%)</t>
+  </si>
+  <si>
+    <t>73(63.5%)</t>
+  </si>
+  <si>
+    <t>75(65.2%)</t>
+  </si>
+  <si>
+    <t>10(8.7%)</t>
+  </si>
+  <si>
+    <t>11(73.3%)</t>
+  </si>
+  <si>
+    <t>79(68.7%)</t>
+  </si>
+  <si>
+    <t>16(13.9%)</t>
+  </si>
+  <si>
+    <t>51(44.3%)</t>
+  </si>
+  <si>
+    <t>41(35.7%)</t>
+  </si>
+  <si>
+    <t>58(50.4%)</t>
+  </si>
+  <si>
+    <t>37(32.2%)</t>
+  </si>
+  <si>
+    <t>46(40.0%)</t>
+  </si>
+  <si>
+    <t>11(9.6%)</t>
+  </si>
+  <si>
+    <t>1(0.9%)</t>
+  </si>
+  <si>
+    <t>21(18.3%)</t>
+  </si>
+  <si>
+    <t>18(15.7%)</t>
+  </si>
+  <si>
+    <t>9(7.8%)</t>
+  </si>
+  <si>
+    <t>3(2.6%)</t>
+  </si>
+  <si>
+    <t>19(16.5%)</t>
+  </si>
+  <si>
+    <t>2(13.3%)</t>
+  </si>
+  <si>
+    <t>5(4.3%)</t>
+  </si>
+  <si>
+    <t>14(12.2%)</t>
+  </si>
+  <si>
+    <t>17(14.8%)</t>
+  </si>
+  <si>
+    <t>7(6.1%)</t>
+  </si>
+  <si>
+    <t>2(1.7%)</t>
+  </si>
+  <si>
+    <t>0(0.0%)</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>C-</t>
+  </si>
+  <si>
+    <t>D+</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>W</t>
   </si>
   <si>
     <t>I-we</t>
-  </si>
-  <si>
-    <t>1(6.7%)</t>
-  </si>
-  <si>
-    <t>20(17.4%)</t>
-  </si>
-  <si>
-    <t>97(84.3%)</t>
-  </si>
-  <si>
-    <t>23(20.0%)</t>
-  </si>
-  <si>
-    <t>24(20.9%)</t>
-  </si>
-  <si>
-    <t>31(27.0%)</t>
-  </si>
-  <si>
-    <t>73(63.5%)</t>
-  </si>
-  <si>
-    <t>75(65.2%)</t>
-  </si>
-  <si>
-    <t>10(8.7%)</t>
-  </si>
-  <si>
-    <t>11(73.3%)</t>
-  </si>
-  <si>
-    <t>79(68.7%)</t>
-  </si>
-  <si>
-    <t>16(13.9%)</t>
-  </si>
-  <si>
-    <t>50(43.5%)</t>
-  </si>
-  <si>
-    <t>41(35.7%)</t>
-  </si>
-  <si>
-    <t>58(50.4%)</t>
-  </si>
-  <si>
-    <t>37(32.2%)</t>
-  </si>
-  <si>
-    <t>46(40.0%)</t>
-  </si>
-  <si>
-    <t>11(9.6%)</t>
-  </si>
-  <si>
-    <t>1(0.9%)</t>
-  </si>
-  <si>
-    <t>22(19.1%)</t>
-  </si>
-  <si>
-    <t>18(15.7%)</t>
-  </si>
-  <si>
-    <t>9(7.8%)</t>
-  </si>
-  <si>
-    <t>3(2.6%)</t>
-  </si>
-  <si>
-    <t>19(16.5%)</t>
-  </si>
-  <si>
-    <t>2(13.3%)</t>
-  </si>
-  <si>
-    <t>5(4.3%)</t>
-  </si>
-  <si>
-    <t>14(12.2%)</t>
-  </si>
-  <si>
-    <t>17(14.8%)</t>
-  </si>
-  <si>
-    <t>7(6.1%)</t>
-  </si>
-  <si>
-    <t>2(1.7%)</t>
-  </si>
-  <si>
-    <t>0(0.0%)</t>
-  </si>
-  <si>
-    <t>21(18.3%)</t>
-  </si>
-  <si>
-    <t>13(11.3%)</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>C-</t>
-  </si>
-  <si>
-    <t>D+</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>W</t>
   </si>
 </sst>
 </file>
@@ -1342,31 +1336,31 @@
         <v>17</v>
       </c>
       <c r="R2" t="s">
+        <v>252</v>
+      </c>
+      <c r="S2" t="s">
         <v>253</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>254</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>255</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>256</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>257</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>258</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>259</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>260</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -1416,31 +1410,31 @@
         <v>22</v>
       </c>
       <c r="R3" t="s">
+        <v>261</v>
+      </c>
+      <c r="S3" t="s">
         <v>262</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>263</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>264</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>265</v>
       </c>
-      <c r="V3" t="s">
+      <c r="W3" t="s">
         <v>266</v>
       </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
+        <v>257</v>
+      </c>
+      <c r="Y3" t="s">
         <v>267</v>
       </c>
-      <c r="X3" t="s">
-        <v>258</v>
-      </c>
-      <c r="Y3" t="s">
+      <c r="Z3" t="s">
         <v>268</v>
-      </c>
-      <c r="Z3" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:26">
@@ -1490,31 +1484,31 @@
         <v>91</v>
       </c>
       <c r="R4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="S4" t="s">
+        <v>269</v>
+      </c>
+      <c r="T4" t="s">
         <v>270</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
         <v>271</v>
       </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
+        <v>255</v>
+      </c>
+      <c r="W4" t="s">
         <v>272</v>
       </c>
-      <c r="V4" t="s">
-        <v>256</v>
-      </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>273</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Y4" t="s">
         <v>274</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>275</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:26">
@@ -1564,31 +1558,31 @@
         <v>122</v>
       </c>
       <c r="R5" t="s">
+        <v>276</v>
+      </c>
+      <c r="S5" t="s">
         <v>277</v>
       </c>
-      <c r="S5" t="s">
+      <c r="T5" t="s">
+        <v>270</v>
+      </c>
+      <c r="U5" t="s">
         <v>278</v>
       </c>
-      <c r="T5" t="s">
+      <c r="V5" t="s">
+        <v>279</v>
+      </c>
+      <c r="W5" t="s">
+        <v>280</v>
+      </c>
+      <c r="X5" t="s">
+        <v>281</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>282</v>
+      </c>
+      <c r="Z5" t="s">
         <v>271</v>
-      </c>
-      <c r="U5" t="s">
-        <v>279</v>
-      </c>
-      <c r="V5" t="s">
-        <v>280</v>
-      </c>
-      <c r="W5" t="s">
-        <v>281</v>
-      </c>
-      <c r="X5" t="s">
-        <v>282</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:26">
@@ -1638,31 +1632,31 @@
         <v>159</v>
       </c>
       <c r="R6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U6" t="s">
+        <v>277</v>
+      </c>
+      <c r="V6" t="s">
+        <v>274</v>
+      </c>
+      <c r="W6" t="s">
+        <v>282</v>
+      </c>
+      <c r="X6" t="s">
+        <v>282</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>282</v>
+      </c>
+      <c r="Z6" t="s">
         <v>278</v>
-      </c>
-      <c r="V6" t="s">
-        <v>275</v>
-      </c>
-      <c r="W6" t="s">
-        <v>283</v>
-      </c>
-      <c r="X6" t="s">
-        <v>283</v>
-      </c>
-      <c r="Y6" t="s">
-        <v>283</v>
-      </c>
-      <c r="Z6" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:26">
@@ -1712,31 +1706,31 @@
         <v>212</v>
       </c>
       <c r="R7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="V7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="W7" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="X7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Y7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Z7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:26">
@@ -1786,31 +1780,31 @@
         <v>237</v>
       </c>
       <c r="R8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Y8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Z8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" spans="1:26">
@@ -1857,34 +1851,34 @@
         <v>8</v>
       </c>
       <c r="Q9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="R9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Y9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Z9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:26">
@@ -1931,34 +1925,34 @@
         <v>9</v>
       </c>
       <c r="Q10" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="R10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Y10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Z10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="11" spans="1:26">
@@ -2005,34 +1999,34 @@
         <v>9</v>
       </c>
       <c r="Q11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="R11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Y11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Z11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="12" spans="1:26">
@@ -2079,34 +2073,34 @@
         <v>11</v>
       </c>
       <c r="Q12" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="R12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Y12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Z12" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:26">
@@ -2153,34 +2147,34 @@
         <v>11</v>
       </c>
       <c r="Q13" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="R13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Y13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Z13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:26">
@@ -2227,34 +2221,34 @@
         <v>11</v>
       </c>
       <c r="Q14" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="R14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Y14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Z14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="15" spans="1:26">
@@ -2301,34 +2295,34 @@
         <v>11</v>
       </c>
       <c r="Q15" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="R15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="S15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="T15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="U15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="W15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="X15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Y15" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="Z15" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:26">
@@ -5211,10 +5205,10 @@
         <v>17</v>
       </c>
       <c r="G81" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="H81" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="I81" t="s">
         <v>22</v>
@@ -5249,16 +5243,16 @@
         <v>16</v>
       </c>
       <c r="E82" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F82" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G82" t="s">
         <v>91</v>
       </c>
       <c r="H82" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="I82" t="s">
         <v>22</v>
@@ -5267,21 +5261,21 @@
         <v>22</v>
       </c>
       <c r="K82" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L82" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="M82">
         <v>3.817</v>
       </c>
       <c r="N82">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B83" t="s">
         <v>182</v>
@@ -5290,16 +5284,16 @@
         <v>183</v>
       </c>
       <c r="D83" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E83" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F83" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G83" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="H83" t="s">
         <v>122</v>
@@ -5308,16 +5302,16 @@
         <v>22</v>
       </c>
       <c r="J83" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K83" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L83" t="s">
-        <v>159</v>
+        <v>22</v>
       </c>
       <c r="M83">
-        <v>3.811</v>
+        <v>3.817</v>
       </c>
       <c r="N83">
         <v>82</v>
@@ -5334,19 +5328,19 @@
         <v>185</v>
       </c>
       <c r="D84" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E84" t="s">
         <v>22</v>
       </c>
       <c r="F84" t="s">
-        <v>122</v>
+        <v>17</v>
       </c>
       <c r="G84" t="s">
         <v>22</v>
       </c>
       <c r="H84" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="I84" t="s">
         <v>22</v>
@@ -5355,13 +5349,13 @@
         <v>17</v>
       </c>
       <c r="K84" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L84" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="M84">
-        <v>3.808</v>
+        <v>3.811</v>
       </c>
       <c r="N84">
         <v>83</v>
@@ -5381,31 +5375,31 @@
         <v>16</v>
       </c>
       <c r="E85" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F85" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="G85" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="H85" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="I85" t="s">
         <v>22</v>
       </c>
       <c r="J85" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="K85" t="s">
         <v>22</v>
       </c>
       <c r="L85" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="M85">
-        <v>3.791</v>
+        <v>3.808</v>
       </c>
       <c r="N85">
         <v>84</v>
@@ -5425,31 +5419,31 @@
         <v>16</v>
       </c>
       <c r="E86" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F86" t="s">
         <v>17</v>
       </c>
       <c r="G86" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="H86" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="I86" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="J86" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="K86" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L86" t="s">
         <v>22</v>
       </c>
       <c r="M86">
-        <v>3.786</v>
+        <v>3.791</v>
       </c>
       <c r="N86">
         <v>85</v>
@@ -5475,25 +5469,25 @@
         <v>17</v>
       </c>
       <c r="G87" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="H87" t="s">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="I87" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="J87" t="s">
         <v>17</v>
       </c>
       <c r="K87" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L87" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="M87">
-        <v>3.778</v>
+        <v>3.786</v>
       </c>
       <c r="N87">
         <v>86</v>
@@ -5519,25 +5513,25 @@
         <v>17</v>
       </c>
       <c r="G88" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="H88" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="I88" t="s">
         <v>22</v>
       </c>
       <c r="J88" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K88" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L88" t="s">
         <v>122</v>
       </c>
       <c r="M88">
-        <v>3.765</v>
+        <v>3.778</v>
       </c>
       <c r="N88">
         <v>87</v>
@@ -6566,34 +6560,34 @@
         <v>243</v>
       </c>
       <c r="D112" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E112" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F112" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G112" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="H112" t="s">
         <v>212</v>
       </c>
       <c r="I112" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="J112" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K112" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="L112" t="s">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="M112">
-        <v>3.459</v>
+        <v>3.46</v>
       </c>
       <c r="N112">
         <v>111</v>
@@ -6610,34 +6604,34 @@
         <v>245</v>
       </c>
       <c r="D113" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E113" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F113" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G113" t="s">
         <v>159</v>
       </c>
       <c r="H113" t="s">
-        <v>122</v>
+        <v>212</v>
       </c>
       <c r="I113" t="s">
         <v>122</v>
       </c>
       <c r="J113" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="K113" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L113" t="s">
-        <v>159</v>
+        <v>212</v>
       </c>
       <c r="M113">
-        <v>3.456</v>
+        <v>3.459</v>
       </c>
       <c r="N113">
         <v>112</v>
@@ -6657,31 +6651,31 @@
         <v>16</v>
       </c>
       <c r="E114" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F114" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G114" t="s">
-        <v>212</v>
+        <v>159</v>
       </c>
       <c r="H114" t="s">
-        <v>212</v>
+        <v>122</v>
       </c>
       <c r="I114" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J114" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="K114" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L114" t="s">
         <v>159</v>
       </c>
       <c r="M114">
-        <v>3.421</v>
+        <v>3.456</v>
       </c>
       <c r="N114">
         <v>113</v>
@@ -6698,34 +6692,34 @@
         <v>249</v>
       </c>
       <c r="D115" t="s">
-        <v>122</v>
+        <v>16</v>
       </c>
       <c r="E115" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="F115" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G115" t="s">
-        <v>122</v>
+        <v>212</v>
       </c>
       <c r="H115" t="s">
         <v>212</v>
       </c>
       <c r="I115" t="s">
-        <v>212</v>
+        <v>91</v>
       </c>
       <c r="J115" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K115" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L115" t="s">
         <v>159</v>
       </c>
       <c r="M115">
-        <v>3.266</v>
+        <v>3.421</v>
       </c>
       <c r="N115">
         <v>114</v>
@@ -6742,10 +6736,10 @@
         <v>251</v>
       </c>
       <c r="D116" t="s">
-        <v>16</v>
+        <v>122</v>
       </c>
       <c r="E116" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="F116" t="s">
         <v>22</v>
@@ -6757,19 +6751,19 @@
         <v>212</v>
       </c>
       <c r="I116" t="s">
-        <v>91</v>
+        <v>212</v>
       </c>
       <c r="J116" t="s">
         <v>17</v>
       </c>
       <c r="K116" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="L116" t="s">
-        <v>252</v>
+        <v>159</v>
       </c>
       <c r="M116">
-        <v>3.069</v>
+        <v>3.266</v>
       </c>
       <c r="N116">
         <v>115</v>

--- a/output/Results - sem2 (Extended).xlsx
+++ b/output/Results - sem2 (Extended).xlsx
@@ -415,6 +415,12 @@
     <t>PITIWADUGE D.N.</t>
   </si>
   <si>
+    <t>230477</t>
+  </si>
+  <si>
+    <t>PERERA H.A.J.I.</t>
+  </si>
+  <si>
     <t>230063</t>
   </si>
   <si>
@@ -544,12 +550,6 @@
     <t>RANAWAKA R.A.G.K.</t>
   </si>
   <si>
-    <t>230477</t>
-  </si>
-  <si>
-    <t>PERERA H.A.J.I.</t>
-  </si>
-  <si>
     <t>230229</t>
   </si>
   <si>
@@ -610,6 +610,12 @@
     <t>INDUWARA M.L.A.S.</t>
   </si>
   <si>
+    <t>230650</t>
+  </si>
+  <si>
+    <t>UBEYSEKARA V.T.T.</t>
+  </si>
+  <si>
     <t>230077</t>
   </si>
   <si>
@@ -634,10 +640,10 @@
     <t>PALIHENA H.H.</t>
   </si>
   <si>
-    <t>230650</t>
-  </si>
-  <si>
-    <t>UBEYSEKARA V.T.T.</t>
+    <t>230327</t>
+  </si>
+  <si>
+    <t>KAUSHALYA R.G.S.P.</t>
   </si>
   <si>
     <t>230175</t>
@@ -655,12 +661,6 @@
     <t>B-</t>
   </si>
   <si>
-    <t>230327</t>
-  </si>
-  <si>
-    <t>KAUSHALYA R.G.S.P.</t>
-  </si>
-  <si>
     <t>230395</t>
   </si>
   <si>
@@ -802,13 +802,13 @@
     <t>11(73.3%)</t>
   </si>
   <si>
-    <t>79(68.7%)</t>
+    <t>81(70.4%)</t>
   </si>
   <si>
     <t>16(13.9%)</t>
   </si>
   <si>
-    <t>51(44.3%)</t>
+    <t>52(45.2%)</t>
   </si>
   <si>
     <t>41(35.7%)</t>
@@ -823,46 +823,46 @@
     <t>46(40.0%)</t>
   </si>
   <si>
-    <t>11(9.6%)</t>
-  </si>
-  <si>
     <t>1(0.9%)</t>
   </si>
   <si>
+    <t>18(15.7%)</t>
+  </si>
+  <si>
+    <t>9(7.8%)</t>
+  </si>
+  <si>
+    <t>3(2.6%)</t>
+  </si>
+  <si>
+    <t>19(16.5%)</t>
+  </si>
+  <si>
+    <t>2(13.3%)</t>
+  </si>
+  <si>
+    <t>4(3.5%)</t>
+  </si>
+  <si>
+    <t>14(12.2%)</t>
+  </si>
+  <si>
+    <t>17(14.8%)</t>
+  </si>
+  <si>
+    <t>7(6.1%)</t>
+  </si>
+  <si>
+    <t>2(1.7%)</t>
+  </si>
+  <si>
+    <t>0(0.0%)</t>
+  </si>
+  <si>
     <t>21(18.3%)</t>
   </si>
   <si>
-    <t>18(15.7%)</t>
-  </si>
-  <si>
-    <t>9(7.8%)</t>
-  </si>
-  <si>
-    <t>3(2.6%)</t>
-  </si>
-  <si>
-    <t>19(16.5%)</t>
-  </si>
-  <si>
-    <t>2(13.3%)</t>
-  </si>
-  <si>
     <t>5(4.3%)</t>
-  </si>
-  <si>
-    <t>14(12.2%)</t>
-  </si>
-  <si>
-    <t>17(14.8%)</t>
-  </si>
-  <si>
-    <t>7(6.1%)</t>
-  </si>
-  <si>
-    <t>2(1.7%)</t>
-  </si>
-  <si>
-    <t>0(0.0%)</t>
   </si>
   <si>
     <t>C</t>
@@ -1487,28 +1487,28 @@
         <v>252</v>
       </c>
       <c r="S4" t="s">
+        <v>260</v>
+      </c>
+      <c r="T4" t="s">
         <v>269</v>
       </c>
-      <c r="T4" t="s">
-        <v>270</v>
-      </c>
       <c r="U4" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="V4" t="s">
         <v>255</v>
       </c>
       <c r="W4" t="s">
+        <v>270</v>
+      </c>
+      <c r="X4" t="s">
+        <v>271</v>
+      </c>
+      <c r="Y4" t="s">
         <v>272</v>
       </c>
-      <c r="X4" t="s">
+      <c r="Z4" t="s">
         <v>273</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>274</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:26">
@@ -1558,31 +1558,31 @@
         <v>122</v>
       </c>
       <c r="R5" t="s">
+        <v>274</v>
+      </c>
+      <c r="S5" t="s">
+        <v>275</v>
+      </c>
+      <c r="T5" t="s">
+        <v>269</v>
+      </c>
+      <c r="U5" t="s">
         <v>276</v>
       </c>
-      <c r="S5" t="s">
+      <c r="V5" t="s">
         <v>277</v>
       </c>
-      <c r="T5" t="s">
-        <v>270</v>
-      </c>
-      <c r="U5" t="s">
+      <c r="W5" t="s">
         <v>278</v>
       </c>
-      <c r="V5" t="s">
+      <c r="X5" t="s">
         <v>279</v>
       </c>
-      <c r="W5" t="s">
-        <v>280</v>
-      </c>
-      <c r="X5" t="s">
+      <c r="Y5" t="s">
+        <v>280</v>
+      </c>
+      <c r="Z5" t="s">
         <v>281</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>282</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:26">
@@ -1629,34 +1629,34 @@
         <v>4</v>
       </c>
       <c r="Q6" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="R6" t="s">
+        <v>280</v>
+      </c>
+      <c r="S6" t="s">
+        <v>280</v>
+      </c>
+      <c r="T6" t="s">
+        <v>280</v>
+      </c>
+      <c r="U6" t="s">
         <v>282</v>
       </c>
-      <c r="S6" t="s">
-        <v>282</v>
-      </c>
-      <c r="T6" t="s">
-        <v>282</v>
-      </c>
-      <c r="U6" t="s">
-        <v>277</v>
-      </c>
       <c r="V6" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="W6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="X6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Y6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:26">
@@ -1703,34 +1703,34 @@
         <v>4</v>
       </c>
       <c r="Q7" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="R7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="S7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="T7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="U7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="V7" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="W7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="X7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Y7" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z7" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:26">
@@ -1780,31 +1780,31 @@
         <v>237</v>
       </c>
       <c r="R8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="S8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="T8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="U8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="V8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="W8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="X8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Y8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:26">
@@ -1854,31 +1854,31 @@
         <v>283</v>
       </c>
       <c r="R9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="S9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="T9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="U9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="V9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="W9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="X9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Y9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:26">
@@ -1928,31 +1928,31 @@
         <v>284</v>
       </c>
       <c r="R10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="S10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="T10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="U10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="V10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="W10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="X10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Y10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11" spans="1:26">
@@ -2002,31 +2002,31 @@
         <v>285</v>
       </c>
       <c r="R11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="S11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="T11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="U11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="V11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="W11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="X11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Y11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z11" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:26">
@@ -2076,31 +2076,31 @@
         <v>286</v>
       </c>
       <c r="R12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="S12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="T12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="U12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="V12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="W12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="X12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Y12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" spans="1:26">
@@ -2150,31 +2150,31 @@
         <v>287</v>
       </c>
       <c r="R13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="S13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="T13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="U13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="V13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="W13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="X13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Y13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z13" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:26">
@@ -2224,31 +2224,31 @@
         <v>288</v>
       </c>
       <c r="R14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="S14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="T14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="U14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="V14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="W14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="X14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Y14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:26">
@@ -2298,31 +2298,31 @@
         <v>289</v>
       </c>
       <c r="R15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="S15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="T15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="U15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="V15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="W15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="X15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Y15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z15" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:26">
@@ -4231,28 +4231,28 @@
         <v>16</v>
       </c>
       <c r="E59" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F59" t="s">
         <v>17</v>
       </c>
       <c r="G59" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="I59" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J59" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K59" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L59" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="M59">
         <v>3.908</v>
@@ -4281,22 +4281,22 @@
         <v>17</v>
       </c>
       <c r="G60" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="H60" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="I60" t="s">
         <v>22</v>
       </c>
       <c r="J60" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K60" t="s">
         <v>17</v>
       </c>
       <c r="L60" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="M60">
         <v>3.908</v>
@@ -4319,13 +4319,13 @@
         <v>16</v>
       </c>
       <c r="E61" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F61" t="s">
         <v>17</v>
       </c>
       <c r="G61" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="H61" t="s">
         <v>22</v>
@@ -4334,13 +4334,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K61" t="s">
         <v>17</v>
       </c>
       <c r="L61" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="M61">
         <v>3.908</v>
@@ -4369,10 +4369,10 @@
         <v>17</v>
       </c>
       <c r="G62" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="H62" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="I62" t="s">
         <v>22</v>
@@ -4384,13 +4384,13 @@
         <v>17</v>
       </c>
       <c r="L62" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="M62">
         <v>3.908</v>
       </c>
       <c r="N62">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="63" spans="1:14">
@@ -4413,28 +4413,28 @@
         <v>17</v>
       </c>
       <c r="G63" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="H63" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="I63" t="s">
         <v>22</v>
       </c>
       <c r="J63" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K63" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L63" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="M63">
         <v>3.908</v>
       </c>
       <c r="N63">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -4463,7 +4463,7 @@
         <v>22</v>
       </c>
       <c r="I64" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="J64" t="s">
         <v>22</v>
@@ -4472,13 +4472,13 @@
         <v>22</v>
       </c>
       <c r="L64" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="M64">
         <v>3.908</v>
       </c>
       <c r="N64">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -4522,12 +4522,12 @@
         <v>3.908</v>
       </c>
       <c r="N65">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B66" t="s">
         <v>147</v>
@@ -4548,25 +4548,25 @@
         <v>22</v>
       </c>
       <c r="H66" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="I66" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="J66" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="K66" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L66" t="s">
         <v>91</v>
       </c>
       <c r="M66">
-        <v>3.895</v>
+        <v>3.908</v>
       </c>
       <c r="N66">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="67" spans="1:14">
@@ -4580,7 +4580,7 @@
         <v>150</v>
       </c>
       <c r="D67" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E67" t="s">
         <v>22</v>
@@ -4598,16 +4598,16 @@
         <v>22</v>
       </c>
       <c r="J67" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="K67" t="s">
         <v>17</v>
       </c>
       <c r="L67" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="M67">
-        <v>3.888</v>
+        <v>3.895</v>
       </c>
       <c r="N67">
         <v>66</v>
@@ -4624,10 +4624,10 @@
         <v>152</v>
       </c>
       <c r="D68" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E68" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F68" t="s">
         <v>17</v>
@@ -4636,13 +4636,13 @@
         <v>22</v>
       </c>
       <c r="H68" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="I68" t="s">
         <v>22</v>
       </c>
       <c r="J68" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="K68" t="s">
         <v>17</v>
@@ -4651,7 +4651,7 @@
         <v>122</v>
       </c>
       <c r="M68">
-        <v>3.882</v>
+        <v>3.888</v>
       </c>
       <c r="N68">
         <v>67</v>
@@ -4668,10 +4668,10 @@
         <v>154</v>
       </c>
       <c r="D69" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E69" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F69" t="s">
         <v>17</v>
@@ -4683,19 +4683,19 @@
         <v>22</v>
       </c>
       <c r="I69" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="J69" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="K69" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L69" t="s">
         <v>122</v>
       </c>
       <c r="M69">
-        <v>3.877</v>
+        <v>3.882</v>
       </c>
       <c r="N69">
         <v>68</v>
@@ -4712,10 +4712,10 @@
         <v>156</v>
       </c>
       <c r="D70" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E70" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F70" t="s">
         <v>17</v>
@@ -4724,10 +4724,10 @@
         <v>22</v>
       </c>
       <c r="H70" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="I70" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="J70" t="s">
         <v>17</v>
@@ -4739,7 +4739,7 @@
         <v>122</v>
       </c>
       <c r="M70">
-        <v>3.869</v>
+        <v>3.877</v>
       </c>
       <c r="N70">
         <v>69</v>
@@ -4747,7 +4747,7 @@
     </row>
     <row r="71" spans="1:14">
       <c r="A71">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B71" t="s">
         <v>157</v>
@@ -4759,7 +4759,7 @@
         <v>16</v>
       </c>
       <c r="E71" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F71" t="s">
         <v>17</v>
@@ -4768,7 +4768,7 @@
         <v>22</v>
       </c>
       <c r="H71" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="I71" t="s">
         <v>17</v>
@@ -4777,10 +4777,10 @@
         <v>17</v>
       </c>
       <c r="K71" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L71" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="M71">
         <v>3.869</v>
@@ -4791,40 +4791,40 @@
     </row>
     <row r="72" spans="1:14">
       <c r="A72">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
+        <v>159</v>
+      </c>
+      <c r="C72" t="s">
         <v>160</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" t="s">
+        <v>22</v>
+      </c>
+      <c r="F72" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72" t="s">
+        <v>22</v>
+      </c>
+      <c r="H72" t="s">
+        <v>22</v>
+      </c>
+      <c r="I72" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" t="s">
+        <v>17</v>
+      </c>
+      <c r="K72" t="s">
+        <v>17</v>
+      </c>
+      <c r="L72" t="s">
         <v>161</v>
-      </c>
-      <c r="D72" t="s">
-        <v>16</v>
-      </c>
-      <c r="E72" t="s">
-        <v>17</v>
-      </c>
-      <c r="F72" t="s">
-        <v>17</v>
-      </c>
-      <c r="G72" t="s">
-        <v>22</v>
-      </c>
-      <c r="H72" t="s">
-        <v>122</v>
-      </c>
-      <c r="I72" t="s">
-        <v>22</v>
-      </c>
-      <c r="J72" t="s">
-        <v>17</v>
-      </c>
-      <c r="K72" t="s">
-        <v>17</v>
-      </c>
-      <c r="L72" t="s">
-        <v>91</v>
       </c>
       <c r="M72">
         <v>3.869</v>
@@ -4835,7 +4835,7 @@
     </row>
     <row r="73" spans="1:14">
       <c r="A73">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B73" t="s">
         <v>162</v>
@@ -4847,7 +4847,7 @@
         <v>16</v>
       </c>
       <c r="E73" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F73" t="s">
         <v>17</v>
@@ -4859,13 +4859,13 @@
         <v>122</v>
       </c>
       <c r="I73" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J73" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K73" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L73" t="s">
         <v>91</v>
@@ -4879,7 +4879,7 @@
     </row>
     <row r="74" spans="1:14">
       <c r="A74">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B74" t="s">
         <v>164</v>
@@ -4897,19 +4897,19 @@
         <v>17</v>
       </c>
       <c r="G74" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="H74" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="I74" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J74" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K74" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L74" t="s">
         <v>91</v>
@@ -4918,12 +4918,12 @@
         <v>3.869</v>
       </c>
       <c r="N74">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B75" t="s">
         <v>166</v>
@@ -4947,22 +4947,22 @@
         <v>91</v>
       </c>
       <c r="I75" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="J75" t="s">
         <v>17</v>
       </c>
       <c r="K75" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L75" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="M75">
-        <v>3.856</v>
+        <v>3.869</v>
       </c>
       <c r="N75">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -4976,7 +4976,7 @@
         <v>169</v>
       </c>
       <c r="D76" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E76" t="s">
         <v>22</v>
@@ -4991,19 +4991,19 @@
         <v>91</v>
       </c>
       <c r="I76" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="J76" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K76" t="s">
         <v>22</v>
       </c>
       <c r="L76" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="M76">
-        <v>3.844</v>
+        <v>3.856</v>
       </c>
       <c r="N76">
         <v>75</v>
@@ -5020,34 +5020,34 @@
         <v>171</v>
       </c>
       <c r="D77" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E77" t="s">
         <v>22</v>
       </c>
       <c r="F77" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G77" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="H77" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="I77" t="s">
         <v>22</v>
       </c>
       <c r="J77" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K77" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L77" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="M77">
-        <v>3.839</v>
+        <v>3.844</v>
       </c>
       <c r="N77">
         <v>76</v>
@@ -5070,13 +5070,13 @@
         <v>22</v>
       </c>
       <c r="F78" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G78" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="H78" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="I78" t="s">
         <v>22</v>
@@ -5088,10 +5088,10 @@
         <v>17</v>
       </c>
       <c r="L78" t="s">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="M78">
-        <v>3.83</v>
+        <v>3.839</v>
       </c>
       <c r="N78">
         <v>77</v>
@@ -5099,7 +5099,7 @@
     </row>
     <row r="79" spans="1:14">
       <c r="A79">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B79" t="s">
         <v>174</v>
@@ -5132,18 +5132,18 @@
         <v>17</v>
       </c>
       <c r="L79" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M79">
         <v>3.83</v>
       </c>
       <c r="N79">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
         <v>176</v>
@@ -5155,39 +5155,39 @@
         <v>16</v>
       </c>
       <c r="E80" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="F80" t="s">
         <v>17</v>
       </c>
       <c r="G80" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="H80" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="I80" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J80" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K80" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L80" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="M80">
-        <v>3.817</v>
+        <v>3.83</v>
       </c>
       <c r="N80">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B81" t="s">
         <v>178</v>
@@ -5231,7 +5231,7 @@
     </row>
     <row r="82" spans="1:14">
       <c r="A82">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B82" t="s">
         <v>180</v>
@@ -5275,7 +5275,7 @@
     </row>
     <row r="83" spans="1:14">
       <c r="A83">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B83" t="s">
         <v>182</v>
@@ -5352,7 +5352,7 @@
         <v>17</v>
       </c>
       <c r="L84" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M84">
         <v>3.811</v>
@@ -5516,7 +5516,7 @@
         <v>22</v>
       </c>
       <c r="H88" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I88" t="s">
         <v>22</v>
@@ -5572,7 +5572,7 @@
         <v>17</v>
       </c>
       <c r="L89" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M89">
         <v>3.756</v>
@@ -5627,7 +5627,7 @@
     </row>
     <row r="91" spans="1:14">
       <c r="A91">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B91" t="s">
         <v>198</v>
@@ -5636,37 +5636,37 @@
         <v>199</v>
       </c>
       <c r="D91" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="E91" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F91" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G91" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="H91" t="s">
         <v>91</v>
       </c>
       <c r="I91" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="J91" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K91" t="s">
         <v>17</v>
       </c>
       <c r="L91" t="s">
-        <v>159</v>
+        <v>91</v>
       </c>
       <c r="M91">
-        <v>3.733</v>
+        <v>3.747</v>
       </c>
       <c r="N91">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="92" spans="1:14">
@@ -5680,19 +5680,19 @@
         <v>201</v>
       </c>
       <c r="D92" t="s">
-        <v>16</v>
+        <v>91</v>
       </c>
       <c r="E92" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="F92" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="G92" t="s">
         <v>91</v>
       </c>
       <c r="H92" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="I92" t="s">
         <v>22</v>
@@ -5704,10 +5704,10 @@
         <v>17</v>
       </c>
       <c r="L92" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M92">
-        <v>3.726</v>
+        <v>3.733</v>
       </c>
       <c r="N92">
         <v>91</v>
@@ -5715,7 +5715,7 @@
     </row>
     <row r="93" spans="1:14">
       <c r="A93">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B93" t="s">
         <v>202</v>
@@ -5736,7 +5736,7 @@
         <v>91</v>
       </c>
       <c r="H93" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="I93" t="s">
         <v>22</v>
@@ -5748,18 +5748,18 @@
         <v>17</v>
       </c>
       <c r="L93" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="M93">
         <v>3.726</v>
       </c>
       <c r="N93">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B94" t="s">
         <v>204</v>
@@ -5771,7 +5771,7 @@
         <v>16</v>
       </c>
       <c r="E94" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F94" t="s">
         <v>17</v>
@@ -5780,25 +5780,25 @@
         <v>91</v>
       </c>
       <c r="H94" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="I94" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="J94" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="K94" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="L94" t="s">
         <v>122</v>
       </c>
       <c r="M94">
-        <v>3.713</v>
+        <v>3.726</v>
       </c>
       <c r="N94">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:14">
@@ -5815,16 +5815,16 @@
         <v>16</v>
       </c>
       <c r="E95" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="F95" t="s">
         <v>17</v>
       </c>
       <c r="G95" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="H95" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="I95" t="s">
         <v>91</v>
@@ -5833,13 +5833,13 @@
         <v>22</v>
       </c>
       <c r="K95" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L95" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="M95">
-        <v>3.708</v>
+        <v>3.713</v>
       </c>
       <c r="N95">
         <v>94</v>
@@ -5865,25 +5865,25 @@
         <v>17</v>
       </c>
       <c r="G96" t="s">
-        <v>122</v>
+        <v>22</v>
       </c>
       <c r="H96" t="s">
         <v>91</v>
       </c>
       <c r="I96" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="J96" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="K96" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="L96" t="s">
-        <v>91</v>
+        <v>161</v>
       </c>
       <c r="M96">
-        <v>3.695</v>
+        <v>3.708</v>
       </c>
       <c r="N96">
         <v>95</v>
@@ -5909,25 +5909,25 @@
         <v>17</v>
       </c>
       <c r="G97" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="H97" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="I97" t="s">
         <v>91</v>
       </c>
       <c r="J97" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="K97" t="s">
-        <v>17</v>
+        <v>91</v>
       </c>
       <c r="L97" t="s">
-        <v>212</v>
+        <v>91</v>
       </c>
       <c r="M97">
-        <v>3.686</v>
+        <v>3.695</v>
       </c>
       <c r="N97">
         <v>96</v>
@@ -5938,40 +5938,40 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>212</v>
+      </c>
+      <c r="C98" t="s">
         <v>213</v>
       </c>
-      <c r="C98" t="s">
+      <c r="D98" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" t="s">
+        <v>22</v>
+      </c>
+      <c r="F98" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98" t="s">
+        <v>22</v>
+      </c>
+      <c r="H98" t="s">
+        <v>122</v>
+      </c>
+      <c r="I98" t="s">
+        <v>91</v>
+      </c>
+      <c r="J98" t="s">
+        <v>17</v>
+      </c>
+      <c r="K98" t="s">
+        <v>17</v>
+      </c>
+      <c r="L98" t="s">
         <v>214</v>
       </c>
-      <c r="D98" t="s">
-        <v>16</v>
-      </c>
-      <c r="E98" t="s">
-        <v>22</v>
-      </c>
-      <c r="F98" t="s">
-        <v>17</v>
-      </c>
-      <c r="G98" t="s">
-        <v>91</v>
-      </c>
-      <c r="H98" t="s">
-        <v>91</v>
-      </c>
-      <c r="I98" t="s">
-        <v>122</v>
-      </c>
-      <c r="J98" t="s">
-        <v>17</v>
-      </c>
-      <c r="K98" t="s">
-        <v>17</v>
-      </c>
-      <c r="L98" t="s">
-        <v>159</v>
-      </c>
       <c r="M98">
-        <v>3.656</v>
+        <v>3.686</v>
       </c>
       <c r="N98">
         <v>97</v>
@@ -5979,7 +5979,7 @@
     </row>
     <row r="99" spans="1:14">
       <c r="A99">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B99" t="s">
         <v>215</v>
@@ -6056,7 +6056,7 @@
         <v>22</v>
       </c>
       <c r="L100" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M100">
         <v>3.634</v>
@@ -6100,7 +6100,7 @@
         <v>22</v>
       </c>
       <c r="L101" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M101">
         <v>3.629</v>
@@ -6129,7 +6129,7 @@
         <v>17</v>
       </c>
       <c r="G102" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H102" t="s">
         <v>91</v>
@@ -6173,10 +6173,10 @@
         <v>17</v>
       </c>
       <c r="G103" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H103" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I103" t="s">
         <v>22</v>
@@ -6217,7 +6217,7 @@
         <v>22</v>
       </c>
       <c r="G104" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H104" t="s">
         <v>91</v>
@@ -6276,7 +6276,7 @@
         <v>22</v>
       </c>
       <c r="L105" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M105">
         <v>3.604</v>
@@ -6396,7 +6396,7 @@
         <v>122</v>
       </c>
       <c r="H108" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I108" t="s">
         <v>22</v>
@@ -6440,7 +6440,7 @@
         <v>122</v>
       </c>
       <c r="H109" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="I109" t="s">
         <v>91</v>
@@ -6528,7 +6528,7 @@
         <v>122</v>
       </c>
       <c r="H111" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I111" t="s">
         <v>22</v>
@@ -6572,7 +6572,7 @@
         <v>122</v>
       </c>
       <c r="H112" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I112" t="s">
         <v>91</v>
@@ -6584,7 +6584,7 @@
         <v>91</v>
       </c>
       <c r="L112" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M112">
         <v>3.46</v>
@@ -6613,10 +6613,10 @@
         <v>17</v>
       </c>
       <c r="G113" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H113" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I113" t="s">
         <v>122</v>
@@ -6628,7 +6628,7 @@
         <v>17</v>
       </c>
       <c r="L113" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M113">
         <v>3.459</v>
@@ -6657,7 +6657,7 @@
         <v>22</v>
       </c>
       <c r="G114" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H114" t="s">
         <v>122</v>
@@ -6672,7 +6672,7 @@
         <v>22</v>
       </c>
       <c r="L114" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M114">
         <v>3.456</v>
@@ -6701,10 +6701,10 @@
         <v>17</v>
       </c>
       <c r="G115" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="H115" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I115" t="s">
         <v>91</v>
@@ -6716,7 +6716,7 @@
         <v>17</v>
       </c>
       <c r="L115" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M115">
         <v>3.421</v>
@@ -6748,10 +6748,10 @@
         <v>122</v>
       </c>
       <c r="H116" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="I116" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J116" t="s">
         <v>17</v>
@@ -6760,7 +6760,7 @@
         <v>22</v>
       </c>
       <c r="L116" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M116">
         <v>3.266</v>
